--- a/salidas/empresas/F.xlsx
+++ b/salidas/empresas/F.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>4.175437927246094</v>
+        <v>4.175436973571777</v>
       </c>
       <c r="C2" t="n">
         <v>8.579999923706055</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>3.429837465286255</v>
+        <v>3.429838895797729</v>
       </c>
       <c r="C5" t="n">
         <v>6.949999809265137</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>3.533472776412964</v>
+        <v>3.533473968505859</v>
       </c>
       <c r="C6" t="n">
         <v>7.159999847412109</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>3.419968128204346</v>
+        <v>3.419968366622925</v>
       </c>
       <c r="C7" t="n">
         <v>6.929999828338623</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>3.31571888923645</v>
+        <v>3.315720081329346</v>
       </c>
       <c r="C8" t="n">
         <v>6.670000076293945</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>4.160803318023682</v>
+        <v>4.160806179046631</v>
       </c>
       <c r="C9" t="n">
         <v>8.369999885559082</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>4.021614074707031</v>
+        <v>4.021614551544189</v>
       </c>
       <c r="C10" t="n">
         <v>8.090000152587891</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>3.733290433883667</v>
+        <v>3.7332923412323</v>
       </c>
       <c r="C13" t="n">
         <v>7.510000228881836</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>3.932134389877319</v>
+        <v>3.932135820388794</v>
       </c>
       <c r="C15" t="n">
         <v>7.909999847412109</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>3.922194480895996</v>
+        <v>3.922192811965942</v>
       </c>
       <c r="C16" t="n">
         <v>7.889999866485596</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>3.996759653091431</v>
+        <v>3.996759176254272</v>
       </c>
       <c r="C17" t="n">
         <v>8.039999961853027</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>4.145892143249512</v>
+        <v>4.145891666412354</v>
       </c>
       <c r="C18" t="n">
         <v>8.340000152587891</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>4.682769775390625</v>
+        <v>4.6827712059021</v>
       </c>
       <c r="C19" t="n">
         <v>9.420000076293945</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>4.230400085449219</v>
+        <v>4.230401515960693</v>
       </c>
       <c r="C20" t="n">
         <v>8.510000228881836</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>3.882424116134644</v>
+        <v>3.882423400878906</v>
       </c>
       <c r="C21" t="n">
         <v>7.809999942779541</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>4.220458507537842</v>
+        <v>4.220458984375</v>
       </c>
       <c r="C22" t="n">
         <v>8.489999771118164</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>3.733290433883667</v>
+        <v>3.7332923412323</v>
       </c>
       <c r="C24" t="n">
         <v>7.510000228881836</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>3.34554648399353</v>
+        <v>3.345547199249268</v>
       </c>
       <c r="C25" t="n">
         <v>6.730000019073486</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>3.300806045532227</v>
+        <v>3.300806522369385</v>
       </c>
       <c r="C26" t="n">
         <v>6.639999866485596</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>3.246123552322388</v>
+        <v>3.246124267578125</v>
       </c>
       <c r="C27" t="n">
         <v>6.53000020980835</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>2.843465328216553</v>
+        <v>2.843466520309448</v>
       </c>
       <c r="C28" t="n">
         <v>5.71999979019165</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>2.391095161437988</v>
+        <v>2.391095876693726</v>
       </c>
       <c r="C31" t="n">
         <v>4.809999942779541</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>2.3861243724823</v>
+        <v>2.386125564575195</v>
       </c>
       <c r="C32" t="n">
         <v>4.800000190734863</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>2.217107534408569</v>
+        <v>2.217107772827148</v>
       </c>
       <c r="C33" t="n">
         <v>4.460000038146973</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>2.584968328475952</v>
+        <v>2.584969520568848</v>
       </c>
       <c r="C34" t="n">
         <v>5.199999809265137</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>1.088669538497925</v>
+        <v>1.088669180870056</v>
       </c>
       <c r="C35" t="n">
         <v>2.190000057220459</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>1.337224364280701</v>
+        <v>1.33722448348999</v>
       </c>
       <c r="C36" t="n">
         <v>2.690000057220459</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>1.138380289077759</v>
+        <v>1.138380527496338</v>
       </c>
       <c r="C37" t="n">
         <v>2.289999961853027</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>0.929594874382019</v>
+        <v>0.9295944571495056</v>
       </c>
       <c r="C38" t="n">
         <v>1.870000004768372</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9942185878753662</v>
+        <v>0.9942185282707214</v>
       </c>
       <c r="C39" t="n">
         <v>2</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>1.307397723197937</v>
+        <v>1.307397603988647</v>
       </c>
       <c r="C40" t="n">
         <v>2.630000114440918</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>2.972714424133301</v>
+        <v>2.972714185714722</v>
       </c>
       <c r="C41" t="n">
         <v>5.980000019073486</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>2.858379125595093</v>
+        <v>2.858378648757935</v>
       </c>
       <c r="C42" t="n">
         <v>5.75</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>3.017454624176025</v>
+        <v>3.017454385757446</v>
       </c>
       <c r="C43" t="n">
         <v>6.070000171661377</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>3.976874351501465</v>
+        <v>3.976874113082886</v>
       </c>
       <c r="C44" t="n">
         <v>8</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>3.778030395507812</v>
+        <v>3.778031587600708</v>
       </c>
       <c r="C45" t="n">
         <v>7.599999904632568</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>3.584158420562744</v>
+        <v>3.584158897399902</v>
       </c>
       <c r="C46" t="n">
         <v>7.210000038146973</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>3.479765892028809</v>
+        <v>3.479765176773071</v>
       </c>
       <c r="C47" t="n">
         <v>7</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>4.419303417205811</v>
+        <v>4.419302463531494</v>
       </c>
       <c r="C48" t="n">
         <v>8.890000343322754</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>4.971091747283936</v>
+        <v>4.97109317779541</v>
       </c>
       <c r="C49" t="n">
         <v>10</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>5.388664722442627</v>
+        <v>5.388665199279785</v>
       </c>
       <c r="C50" t="n">
         <v>10.84000015258789</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>5.836063385009766</v>
+        <v>5.836064338684082</v>
       </c>
       <c r="C51" t="n">
         <v>11.73999977111816</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>6.248665332794189</v>
+        <v>6.248663902282715</v>
       </c>
       <c r="C52" t="n">
         <v>12.56999969482422</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>6.472363948822021</v>
+        <v>6.472362041473389</v>
       </c>
       <c r="C53" t="n">
         <v>13.02000045776367</v>
@@ -1524,7 +1536,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>5.0108642578125</v>
+        <v>5.010862350463867</v>
       </c>
       <c r="C55" t="n">
         <v>10.07999992370605</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>6.348085880279541</v>
+        <v>6.348089218139648</v>
       </c>
       <c r="C56" t="n">
         <v>12.77000045776367</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>5.612363815307617</v>
+        <v>5.612365245819092</v>
       </c>
       <c r="C57" t="n">
         <v>11.28999996185303</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>6.084619522094727</v>
+        <v>6.084618091583252</v>
       </c>
       <c r="C58" t="n">
         <v>12.23999977111816</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>7.024154186248779</v>
+        <v>7.024156093597412</v>
       </c>
       <c r="C59" t="n">
         <v>14.13000011444092</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>7.923923492431641</v>
+        <v>7.923923015594482</v>
       </c>
       <c r="C60" t="n">
         <v>15.9399995803833</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>8.346467971801758</v>
+        <v>8.346466064453125</v>
       </c>
       <c r="C61" t="n">
         <v>16.79000091552734</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>7.928893089294434</v>
+        <v>7.928893566131592</v>
       </c>
       <c r="C62" t="n">
         <v>15.94999980926514</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>7.481492519378662</v>
+        <v>7.481495380401611</v>
       </c>
       <c r="C63" t="n">
         <v>15.05000019073486</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>7.411900997161865</v>
+        <v>7.411902904510498</v>
       </c>
       <c r="C64" t="n">
         <v>14.90999984741211</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>7.690283298492432</v>
+        <v>7.690284252166748</v>
       </c>
       <c r="C65" t="n">
         <v>15.47000026702881</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>7.416871547698975</v>
+        <v>7.416871070861816</v>
       </c>
       <c r="C66" t="n">
         <v>14.92000007629395</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>6.855137825012207</v>
+        <v>6.855138301849365</v>
       </c>
       <c r="C67" t="n">
         <v>13.78999996185303</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>6.069705009460449</v>
+        <v>6.069705963134766</v>
       </c>
       <c r="C68" t="n">
         <v>12.21000003814697</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>5.527858257293701</v>
+        <v>5.52785587310791</v>
       </c>
       <c r="C69" t="n">
         <v>11.11999988555908</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>4.807046413421631</v>
+        <v>4.807046890258789</v>
       </c>
       <c r="C70" t="n">
         <v>9.670000076293945</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>5.806237697601318</v>
+        <v>5.806239128112793</v>
       </c>
       <c r="C71" t="n">
         <v>11.68000030517578</v>
@@ -2010,7 +2022,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>5.348897457122803</v>
+        <v>5.348897933959961</v>
       </c>
       <c r="C73" t="n">
         <v>10.76000022888184</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>6.198328971862793</v>
+        <v>6.198330879211426</v>
       </c>
       <c r="C74" t="n">
         <v>12.42000007629395</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>6.178366184234619</v>
+        <v>6.178366661071777</v>
       </c>
       <c r="C75" t="n">
         <v>12.38000011444092</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>6.228271007537842</v>
+        <v>6.228271961212158</v>
       </c>
       <c r="C76" t="n">
         <v>12.47999954223633</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>5.653770446777344</v>
+        <v>5.653770923614502</v>
       </c>
       <c r="C77" t="n">
         <v>11.27999973297119</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>5.292891025543213</v>
+        <v>5.292891502380371</v>
       </c>
       <c r="C78" t="n">
         <v>10.5600004196167</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>4.806707859039307</v>
+        <v>4.806709289550781</v>
       </c>
       <c r="C79" t="n">
         <v>9.590000152587891</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>4.631279945373535</v>
+        <v>4.631280422210693</v>
       </c>
       <c r="C80" t="n">
         <v>9.239999771118164</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>4.70687198638916</v>
+        <v>4.706872463226318</v>
       </c>
       <c r="C81" t="n">
         <v>9.340000152587891</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>4.968925952911377</v>
+        <v>4.968924999237061</v>
       </c>
       <c r="C82" t="n">
         <v>9.859999656677246</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>5.651331901550293</v>
+        <v>5.651332855224609</v>
       </c>
       <c r="C83" t="n">
         <v>11.15999984741211</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>5.798184394836426</v>
+        <v>5.798186302185059</v>
       </c>
       <c r="C84" t="n">
         <v>11.44999980926514</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>6.5577712059021</v>
+        <v>6.557775020599365</v>
       </c>
       <c r="C85" t="n">
         <v>12.94999980926514</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>6.606062889099121</v>
+        <v>6.606064319610596</v>
       </c>
       <c r="C86" t="n">
         <v>12.94999980926514</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>6.432621479034424</v>
+        <v>6.432622909545898</v>
       </c>
       <c r="C87" t="n">
         <v>12.60999965667725</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>6.708086013793945</v>
+        <v>6.708085536956787</v>
       </c>
       <c r="C88" t="n">
         <v>13.14999961853027</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>6.99375581741333</v>
+        <v>6.993755340576172</v>
       </c>
       <c r="C89" t="n">
         <v>13.71000003814697</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>8.057465553283691</v>
+        <v>8.057463645935059</v>
       </c>
       <c r="C90" t="n">
         <v>15.68000030517578</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>7.949551105499268</v>
+        <v>7.949551582336426</v>
       </c>
       <c r="C91" t="n">
         <v>15.47000026702881</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>8.725188255310059</v>
+        <v>8.725191116333008</v>
       </c>
       <c r="C92" t="n">
         <v>16.8799991607666</v>
@@ -2619,7 +2631,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>8.720017433166504</v>
+        <v>8.720020294189453</v>
       </c>
       <c r="C94" t="n">
         <v>16.8700008392334</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>8.894584655761719</v>
+        <v>8.894583702087402</v>
       </c>
       <c r="C95" t="n">
         <v>17.11000061035156</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>8.878987312316895</v>
+        <v>8.878990173339844</v>
       </c>
       <c r="C96" t="n">
         <v>17.07999992370605</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>8.021243095397949</v>
+        <v>8.021242141723633</v>
       </c>
       <c r="C97" t="n">
         <v>15.43000030517578</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>7.839245796203613</v>
+        <v>7.839247703552246</v>
       </c>
       <c r="C98" t="n">
         <v>14.96000003814697</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>8.064576148986816</v>
+        <v>8.064574241638184</v>
       </c>
       <c r="C99" t="n">
         <v>15.39000034332275</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>8.174617767333984</v>
+        <v>8.174614906311035</v>
       </c>
       <c r="C100" t="n">
         <v>15.60000038146973</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>8.528964042663574</v>
+        <v>8.528959274291992</v>
       </c>
       <c r="C101" t="n">
         <v>16.14999961853027</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>8.682114601135254</v>
+        <v>8.682113647460938</v>
       </c>
       <c r="C102" t="n">
         <v>16.44000053405762</v>
@@ -2909,7 +2921,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2938,7 +2950,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>9.260258674621582</v>
+        <v>9.260261535644531</v>
       </c>
       <c r="C105" t="n">
         <v>17.40999984741211</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>7.866698265075684</v>
+        <v>7.866698741912842</v>
       </c>
       <c r="C106" t="n">
         <v>14.78999996185303</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>7.561120510101318</v>
+        <v>7.561120986938477</v>
       </c>
       <c r="C107" t="n">
         <v>14.09000015258789</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>8.441196441650391</v>
+        <v>8.441194534301758</v>
       </c>
       <c r="C108" t="n">
         <v>15.72999954223633</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>8.31777286529541</v>
+        <v>8.317770004272461</v>
       </c>
       <c r="C109" t="n">
         <v>15.5</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>7.974380493164062</v>
+        <v>7.974380970001221</v>
       </c>
       <c r="C110" t="n">
         <v>14.71000003814697</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>8.858017921447754</v>
+        <v>8.858013153076172</v>
       </c>
       <c r="C111" t="n">
         <v>16.34000015258789</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>8.749593734741211</v>
+        <v>8.749591827392578</v>
       </c>
       <c r="C112" t="n">
         <v>16.13999938964844</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>8.646031379699707</v>
+        <v>8.646029472351074</v>
       </c>
       <c r="C113" t="n">
         <v>15.80000019073486</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>8.30128288269043</v>
+        <v>8.301284790039062</v>
       </c>
       <c r="C114" t="n">
         <v>15.17000007629395</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>8.21373176574707</v>
+        <v>8.213728904724121</v>
       </c>
       <c r="C115" t="n">
         <v>15.01000022888184</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>8.198152542114258</v>
+        <v>8.198151588439941</v>
       </c>
       <c r="C116" t="n">
         <v>14.82999992370605</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>7.667454719543457</v>
+        <v>7.667455196380615</v>
       </c>
       <c r="C117" t="n">
         <v>13.86999988555908</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>7.501613140106201</v>
+        <v>7.501611709594727</v>
       </c>
       <c r="C118" t="n">
         <v>13.56999969482422</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>8.270413398742676</v>
+        <v>8.270411491394043</v>
       </c>
       <c r="C119" t="n">
         <v>14.8100004196167</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>8.002362251281738</v>
+        <v>8.002364158630371</v>
       </c>
       <c r="C120" t="n">
         <v>14.32999992370605</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>7.868339538574219</v>
+        <v>7.868337154388428</v>
       </c>
       <c r="C121" t="n">
         <v>14.09000015258789</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>6.892585277557373</v>
+        <v>6.892587184906006</v>
       </c>
       <c r="C122" t="n">
         <v>11.9399995803833</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>7.221626758575439</v>
+        <v>7.22162914276123</v>
       </c>
       <c r="C123" t="n">
         <v>12.51000022888184</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>7.793120384216309</v>
+        <v>7.793124198913574</v>
       </c>
       <c r="C124" t="n">
         <v>13.5</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>7.914098262786865</v>
+        <v>7.914095401763916</v>
       </c>
       <c r="C125" t="n">
         <v>13.5600004196167</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>7.873240947723389</v>
+        <v>7.873239517211914</v>
       </c>
       <c r="C126" t="n">
         <v>13.48999977111816</v>
@@ -3605,7 +3617,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>7.469841003417969</v>
+        <v>7.469842910766602</v>
       </c>
       <c r="C128" t="n">
         <v>12.65999984741211</v>
@@ -3663,7 +3675,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>7.121720790863037</v>
+        <v>7.12172269821167</v>
       </c>
       <c r="C130" t="n">
         <v>12.06999969482422</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>7.013308525085449</v>
+        <v>7.013309955596924</v>
       </c>
       <c r="C131" t="n">
         <v>11.73999977111816</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>7.144734382629395</v>
+        <v>7.144733428955078</v>
       </c>
       <c r="C132" t="n">
         <v>11.96000003814697</v>
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>7.246290683746338</v>
+        <v>7.246289730072021</v>
       </c>
       <c r="C133" t="n">
         <v>12.13000011444092</v>
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>7.502685070037842</v>
+        <v>7.502684593200684</v>
       </c>
       <c r="C134" t="n">
         <v>12.35999965667725</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>7.605875015258789</v>
+        <v>7.605876922607422</v>
       </c>
       <c r="C135" t="n">
         <v>12.52999973297119</v>
@@ -3866,11 +3878,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>7.065636157989502</v>
+        <v>7.065633773803711</v>
       </c>
       <c r="C136" t="n">
         <v>11.64000034332275</v>
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>7.056276321411133</v>
+        <v>7.056278705596924</v>
       </c>
       <c r="C137" t="n">
         <v>11.47000026702881</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>6.840958118438721</v>
+        <v>6.840958595275879</v>
       </c>
       <c r="C138" t="n">
         <v>11.11999988555908</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>6.884022235870361</v>
+        <v>6.884020805358887</v>
       </c>
       <c r="C139" t="n">
         <v>11.1899995803833</v>
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>6.991122245788574</v>
+        <v>6.991123199462891</v>
       </c>
       <c r="C140" t="n">
         <v>11.22000026702881</v>
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>6.872734546661377</v>
+        <v>6.872732639312744</v>
       </c>
       <c r="C141" t="n">
         <v>11.02999973297119</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>7.458442687988281</v>
+        <v>7.458445072174072</v>
       </c>
       <c r="C142" t="n">
         <v>11.97000026702881</v>
@@ -4069,7 +4081,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>7.898014068603516</v>
+        <v>7.898015022277832</v>
       </c>
       <c r="C144" t="n">
         <v>12.52000045776367</v>
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>7.879090785980225</v>
+        <v>7.879087924957275</v>
       </c>
       <c r="C145" t="n">
         <v>12.48999977111816</v>
@@ -4156,7 +4168,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>6.857951164245605</v>
+        <v>6.857951641082764</v>
       </c>
       <c r="C147" t="n">
         <v>10.60999965667725</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>7.161742687225342</v>
+        <v>7.161741733551025</v>
       </c>
       <c r="C148" t="n">
         <v>11.07999992370605</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>7.362637519836426</v>
+        <v>7.362636566162109</v>
       </c>
       <c r="C149" t="n">
         <v>11.23999977111816</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>7.565700054168701</v>
+        <v>7.565699577331543</v>
       </c>
       <c r="C150" t="n">
         <v>11.55000019073486</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>7.251281261444092</v>
+        <v>7.25128173828125</v>
       </c>
       <c r="C151" t="n">
         <v>11.06999969482422</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>6.669046878814697</v>
+        <v>6.669044971466064</v>
       </c>
       <c r="C152" t="n">
         <v>10.03999996185303</v>
@@ -4359,7 +4371,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>6.144289016723633</v>
+        <v>6.144290447235107</v>
       </c>
       <c r="C154" t="n">
         <v>9.25</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>6.457521915435791</v>
+        <v>6.457520008087158</v>
       </c>
       <c r="C155" t="n">
         <v>9.550000190734863</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>6.362855911254883</v>
+        <v>6.362854957580566</v>
       </c>
       <c r="C156" t="n">
         <v>9.409999847412109</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>5.172778606414795</v>
+        <v>5.172779083251953</v>
       </c>
       <c r="C157" t="n">
         <v>7.650000095367432</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>6.054050922393799</v>
+        <v>6.054050445556641</v>
       </c>
       <c r="C158" t="n">
         <v>8.800000190734863</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>6.033411026000977</v>
+        <v>6.033412456512451</v>
       </c>
       <c r="C159" t="n">
         <v>8.770000457763672</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>6.040291309356689</v>
+        <v>6.040290832519531</v>
       </c>
       <c r="C160" t="n">
         <v>8.779999732971191</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>7.304519176483154</v>
+        <v>7.304520606994629</v>
       </c>
       <c r="C161" t="n">
         <v>10.44999980926514</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>6.654451847076416</v>
+        <v>6.654453754425049</v>
       </c>
       <c r="C162" t="n">
         <v>9.520000457763672</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>7.150741577148438</v>
+        <v>7.150739192962646</v>
       </c>
       <c r="C163" t="n">
         <v>10.22999954223633</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>6.760866165161133</v>
+        <v>6.760867595672607</v>
       </c>
       <c r="C164" t="n">
         <v>9.529999732971191</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>6.505471706390381</v>
+        <v>6.505472660064697</v>
       </c>
       <c r="C165" t="n">
         <v>9.170000076293945</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>6.498376846313477</v>
+        <v>6.498377323150635</v>
       </c>
       <c r="C166" t="n">
         <v>9.159999847412109</v>
@@ -4765,7 +4777,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>6.532918930053711</v>
+        <v>6.532918453216553</v>
       </c>
       <c r="C168" t="n">
         <v>9.060000419616699</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>6.705976009368896</v>
+        <v>6.705974102020264</v>
       </c>
       <c r="C169" t="n">
         <v>9.300000190734863</v>
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>6.468019008636475</v>
+        <v>6.468019485473633</v>
       </c>
       <c r="C170" t="n">
         <v>8.819999694824219</v>
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>5.104017734527588</v>
+        <v>5.10401725769043</v>
       </c>
       <c r="C171" t="n">
         <v>6.960000038146973</v>
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>3.542011260986328</v>
+        <v>3.542011976242065</v>
       </c>
       <c r="C172" t="n">
         <v>4.829999923706055</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>3.732678651809692</v>
+        <v>3.732678174972534</v>
       </c>
       <c r="C173" t="n">
         <v>5.090000152587891</v>
@@ -4966,7 +4978,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4993,7 +5005,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5020,7 +5032,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5047,7 +5059,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5074,11 +5086,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>4.884015083312988</v>
+        <v>4.884015560150146</v>
       </c>
       <c r="C178" t="n">
         <v>6.659999847412109</v>
@@ -5101,11 +5113,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>5.668684482574463</v>
+        <v>5.668685436248779</v>
       </c>
       <c r="C179" t="n">
         <v>7.730000019073486</v>
@@ -5128,11 +5140,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>6.658689498901367</v>
+        <v>6.658689022064209</v>
       </c>
       <c r="C180" t="n">
         <v>9.079999923706055</v>
@@ -5155,11 +5167,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>6.446020126342773</v>
+        <v>6.44602108001709</v>
       </c>
       <c r="C181" t="n">
         <v>8.789999961853027</v>
@@ -5182,11 +5194,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>7.722026824951172</v>
+        <v>7.722024917602539</v>
       </c>
       <c r="C182" t="n">
         <v>10.52999973297119</v>
@@ -5209,11 +5221,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>8.580028533935547</v>
+        <v>8.580029487609863</v>
       </c>
       <c r="C183" t="n">
         <v>11.69999980926514</v>
@@ -5236,11 +5248,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>8.983362197875977</v>
+        <v>8.983363151550293</v>
       </c>
       <c r="C184" t="n">
         <v>12.25</v>
@@ -5263,7 +5275,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5292,7 +5304,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5321,11 +5333,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>10.89736843109131</v>
+        <v>10.89737033843994</v>
       </c>
       <c r="C187" t="n">
         <v>14.85999965667725</v>
@@ -5350,11 +5362,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>10.23003196716309</v>
+        <v>10.23003387451172</v>
       </c>
       <c r="C188" t="n">
         <v>13.94999980926514</v>
@@ -5379,7 +5391,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5408,7 +5420,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5437,11 +5449,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>12.5253734588623</v>
+        <v>12.52537250518799</v>
       </c>
       <c r="C191" t="n">
         <v>17.07999992370605</v>
@@ -5466,11 +5478,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>14.14357471466064</v>
+        <v>14.14357376098633</v>
       </c>
       <c r="C192" t="n">
         <v>19.19000053405762</v>
@@ -5495,7 +5507,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5524,7 +5536,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5553,7 +5565,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5582,11 +5594,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>12.52722549438477</v>
+        <v>12.52722454071045</v>
       </c>
       <c r="C196" t="n">
         <v>16.90999984741211</v>
@@ -5611,11 +5623,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>10.55977058410645</v>
+        <v>10.55976963043213</v>
       </c>
       <c r="C197" t="n">
         <v>14.15999984741211</v>
@@ -5640,11 +5652,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>10.20181560516357</v>
+        <v>10.20181274414062</v>
       </c>
       <c r="C198" t="n">
         <v>13.68000030517578</v>
@@ -5669,11 +5681,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>8.300158500671387</v>
+        <v>8.30016040802002</v>
       </c>
       <c r="C199" t="n">
         <v>11.13000011444092</v>
@@ -5698,11 +5710,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>10.95501518249512</v>
+        <v>10.95501708984375</v>
       </c>
       <c r="C200" t="n">
         <v>14.6899995803833</v>
@@ -5727,11 +5739,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>11.4785270690918</v>
+        <v>11.47852897644043</v>
       </c>
       <c r="C201" t="n">
         <v>15.23999977111816</v>
@@ -5756,11 +5768,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>8.435663223266602</v>
+        <v>8.435661315917969</v>
       </c>
       <c r="C202" t="n">
         <v>11.19999980926514</v>
@@ -5785,7 +5797,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5814,11 +5826,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>10.57869434356689</v>
+        <v>10.57869529724121</v>
       </c>
       <c r="C204" t="n">
         <v>13.89999961853027</v>
@@ -5843,11 +5855,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>8.851094245910645</v>
+        <v>8.851095199584961</v>
       </c>
       <c r="C205" t="n">
         <v>11.63000011444092</v>
@@ -5872,11 +5884,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>10.28188323974609</v>
+        <v>10.28188133239746</v>
       </c>
       <c r="C206" t="n">
         <v>13.51000022888184</v>
@@ -5901,11 +5913,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>9.765058517456055</v>
+        <v>9.765057563781738</v>
       </c>
       <c r="C207" t="n">
         <v>12.06999969482422</v>
@@ -5928,11 +5940,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>10.19384860992432</v>
+        <v>10.19384956359863</v>
       </c>
       <c r="C208" t="n">
         <v>12.60000038146973</v>
@@ -5955,11 +5967,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>9.73138427734375</v>
+        <v>9.731383323669434</v>
       </c>
       <c r="C209" t="n">
         <v>11.88000011444092</v>
@@ -5982,11 +5994,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>9.829679489135742</v>
+        <v>9.829680442810059</v>
       </c>
       <c r="C210" t="n">
         <v>12</v>
@@ -6011,11 +6023,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>12.39358901977539</v>
+        <v>12.39358806610107</v>
       </c>
       <c r="C211" t="n">
         <v>15.13000011444092</v>
@@ -6040,11 +6052,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>10.93863010406494</v>
+        <v>10.93862819671631</v>
       </c>
       <c r="C212" t="n">
         <v>13.21000003814697</v>
@@ -6069,11 +6081,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>10.0443286895752</v>
+        <v>10.04432773590088</v>
       </c>
       <c r="C213" t="n">
         <v>12.13000011444092</v>
@@ -6098,11 +6110,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>10.28446388244629</v>
+        <v>10.28446483612061</v>
       </c>
       <c r="C214" t="n">
         <v>12.42000007629395</v>
@@ -6127,11 +6139,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>8.19943904876709</v>
+        <v>8.199440002441406</v>
       </c>
       <c r="C215" t="n">
         <v>9.75</v>
@@ -6156,11 +6168,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>8.62833309173584</v>
+        <v>8.628335952758789</v>
       </c>
       <c r="C216" t="n">
         <v>10.26000022888184</v>
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6214,7 +6226,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6243,7 +6255,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6272,11 +6284,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>11.46940231323242</v>
+        <v>11.46940326690674</v>
       </c>
       <c r="C220" t="n">
         <v>13.27999973297119</v>
@@ -6301,7 +6313,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6330,11 +6342,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>10.60343647003174</v>
+        <v>10.60343551635742</v>
       </c>
       <c r="C222" t="n">
         <v>12.13000011444092</v>
@@ -6359,11 +6371,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>10.961838722229</v>
+        <v>10.96183776855469</v>
       </c>
       <c r="C223" t="n">
         <v>12.53999996185303</v>
@@ -6388,7 +6400,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6417,7 +6429,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6446,7 +6458,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6475,7 +6487,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6504,7 +6516,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6533,11 +6545,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>8.908294677734375</v>
+        <v>8.908293724060059</v>
       </c>
       <c r="C229" t="n">
         <v>9.899999618530273</v>
@@ -6562,7 +6574,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6591,11 +6603,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>8.874185562133789</v>
+        <v>8.874184608459473</v>
       </c>
       <c r="C231" t="n">
         <v>9.550000190734863</v>
@@ -6620,11 +6632,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>9.320216178894043</v>
+        <v>9.320217132568359</v>
       </c>
       <c r="C232" t="n">
         <v>10.02999973297119</v>
@@ -6649,7 +6661,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6678,11 +6690,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>9.786189079284668</v>
+        <v>9.786190032958984</v>
       </c>
       <c r="C234" t="n">
         <v>10.38000011444092</v>
@@ -6707,11 +6719,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>10.22930335998535</v>
+        <v>10.22930240631104</v>
       </c>
       <c r="C235" t="n">
         <v>10.85000038146973</v>
@@ -6736,7 +6748,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6765,7 +6777,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6794,7 +6806,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6823,7 +6835,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6852,7 +6864,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6881,7 +6893,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6910,7 +6922,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6939,11 +6951,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>13.76552104949951</v>
+        <v>13.7655200958252</v>
       </c>
       <c r="C243" t="n">
         <v>14.09000015258789</v>
@@ -6966,11 +6978,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>11.274245262146</v>
+        <v>11.27424430847168</v>
       </c>
       <c r="C244" t="n">
         <v>11.53999996185303</v>
@@ -6993,11 +7005,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>11.80180931091309</v>
+        <v>11.80180835723877</v>
       </c>
       <c r="C245" t="n">
         <v>12.07999992370605</v>
@@ -7020,7 +7032,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7047,7 +7059,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7074,7 +7086,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7101,7 +7113,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7128,17 +7140,17 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>12.9399995803833</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="C250" t="n">
-        <v>12.9399995803833</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="D250" t="n">
-        <v>809754900</v>
+        <v>862159500</v>
       </c>
       <c r="E250" t="n">
         <v>-1.87</v>
@@ -7148,10 +7160,10 @@
         <v>3991000000</v>
       </c>
       <c r="H250" t="n">
-        <v>51643538325.30975</v>
+        <v>50286601522.44568</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2028952392883989</v>
+        <v>0.2160259333500376</v>
       </c>
     </row>
   </sheetData>
@@ -7183,75 +7195,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7287,13 +7299,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7329,13 +7341,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7371,13 +7383,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7413,13 +7425,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7455,13 +7467,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7497,13 +7509,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7539,13 +7551,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7614,7 +7626,7 @@
       <c r="I10" t="n">
         <v>1.66</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I11" t="n">
         <v>1.77</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="K11" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I12" t="n">
         <v>1.75</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K12" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I13" t="n">
         <v>1.73</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K13" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I14" t="n">
         <v>4.94</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="K14" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I15" t="n">
         <v>4.680000000000001</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K15" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I16" t="n">
         <v>4.350000000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="K16" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I17" t="n">
         <v>4.350000000000001</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K17" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I18" t="n">
         <v>1.42</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="K18" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I19" t="n">
         <v>1.47</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="K19" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I20" t="n">
         <v>1.51</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="K20" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I21" t="n">
         <v>1.41</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="K21" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41688</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I22" t="n">
         <v>1.76</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41688</v>
       </c>
       <c r="K22" t="n">
@@ -8179,13 +8191,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8212,7 +8224,7 @@
       <c r="I23" t="n">
         <v>1.600000000000001</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="K23" t="n">
@@ -8225,13 +8237,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8258,7 +8270,7 @@
       <c r="I24" t="n">
         <v>1.620000000000001</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K24" t="n">
@@ -8271,13 +8283,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8304,7 +8316,7 @@
       <c r="I25" t="n">
         <v>1.52</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="K25" t="n">
@@ -8317,13 +8329,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8350,7 +8362,7 @@
       <c r="I26" t="n">
         <v>0.8000000000000005</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="K26" t="n">
@@ -8363,13 +8375,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8396,7 +8408,7 @@
       <c r="I27" t="n">
         <v>0.7900000000000005</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="K27" t="n">
@@ -8409,13 +8421,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8442,7 +8454,7 @@
       <c r="I28" t="n">
         <v>0.9400000000000004</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="K28" t="n">
@@ -8455,13 +8467,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8488,7 +8500,7 @@
       <c r="I29" t="n">
         <v>1.21</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="K29" t="n">
@@ -8501,13 +8513,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8534,7 +8546,7 @@
       <c r="I30" t="n">
         <v>1.840000000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K30" t="n">
@@ -8547,13 +8559,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8580,7 +8592,7 @@
       <c r="I31" t="n">
         <v>2.220000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="K31" t="n">
@@ -8593,13 +8605,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8626,7 +8638,7 @@
       <c r="I32" t="n">
         <v>2.240000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K32" t="n">
@@ -8639,13 +8651,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8672,7 +8684,7 @@
       <c r="I33" t="n">
         <v>2</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="K33" t="n">
@@ -8685,13 +8697,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8718,7 +8730,7 @@
       <c r="I34" t="n">
         <v>1.15</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="K34" t="n">
@@ -8731,13 +8743,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8764,7 +8776,7 @@
       <c r="I35" t="n">
         <v>0.9400000000000003</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K35" t="n">
@@ -8777,13 +8789,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8810,7 +8822,7 @@
       <c r="I36" t="n">
         <v>0.9600000000000003</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="K36" t="n">
@@ -8823,13 +8835,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8856,7 +8868,7 @@
       <c r="I37" t="n">
         <v>1.11</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K37" t="n">
@@ -8869,13 +8881,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8902,7 +8914,7 @@
       <c r="I38" t="n">
         <v>1.9</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="K38" t="n">
@@ -8915,13 +8927,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8948,7 +8960,7 @@
       <c r="I39" t="n">
         <v>1.93</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K39" t="n">
@@ -8961,13 +8973,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8994,7 +9006,7 @@
       <c r="I40" t="n">
         <v>1.69</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K40" t="n">
@@ -9007,13 +9019,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9040,7 +9052,7 @@
       <c r="I41" t="n">
         <v>1.55</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="K41" t="n">
@@ -9053,13 +9065,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9086,7 +9098,7 @@
       <c r="I42" t="n">
         <v>0.9200000000000006</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K42" t="n">
@@ -9099,13 +9111,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9132,7 +9144,7 @@
       <c r="I43" t="n">
         <v>0.7800000000000005</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K43" t="n">
@@ -9145,13 +9157,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9178,7 +9190,7 @@
       <c r="I44" t="n">
         <v>0.5500000000000005</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="K44" t="n">
@@ -9191,13 +9203,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9224,7 +9236,7 @@
       <c r="I45" t="n">
         <v>0.4100000000000005</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="K45" t="n">
@@ -9237,13 +9249,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9270,7 +9282,7 @@
       <c r="I46" t="n">
         <v>0.01000000000000045</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="K46" t="n">
@@ -9283,13 +9295,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9316,7 +9328,7 @@
       <c r="I47" t="n">
         <v>-0.7799999999999996</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K47" t="n">
@@ -9329,13 +9341,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9362,7 +9374,7 @@
       <c r="I48" t="n">
         <v>-0.5399999999999996</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K48" t="n">
@@ -9375,13 +9387,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9408,7 +9420,7 @@
       <c r="I49" t="n">
         <v>-0.0499999999999996</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K49" t="n">
@@ -9421,13 +9433,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="I50" t="n">
         <v>-0.3199999999999996</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="K50" t="n">
@@ -9467,13 +9479,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9500,7 +9512,7 @@
       <c r="I51" t="n">
         <v>0.9900000000000004</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K51" t="n">
@@ -9513,13 +9525,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="I52" t="n">
         <v>0.8500000000000004</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K52" t="n">
@@ -9559,13 +9571,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9592,7 +9604,7 @@
       <c r="I53" t="n">
         <v>0.7000000000000004</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K53" t="n">
@@ -9605,13 +9617,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9638,7 +9650,7 @@
       <c r="I54" t="n">
         <v>4.45</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="K54" t="n">
@@ -9651,13 +9663,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9684,7 +9696,7 @@
       <c r="I55" t="n">
         <v>2.86</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K55" t="n">
@@ -9697,13 +9709,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9730,7 +9742,7 @@
       <c r="I56" t="n">
         <v>2.88</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K56" t="n">
@@ -9743,13 +9755,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="I57" t="n">
         <v>2.22</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K57" t="n">
@@ -9789,13 +9801,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9822,7 +9834,7 @@
       <c r="I58" t="n">
         <v>-0.4899999999999996</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="K58" t="n">
@@ -9835,13 +9847,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9868,7 +9880,7 @@
       <c r="I59" t="n">
         <v>0.7300000000000004</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K59" t="n">
@@ -9881,13 +9893,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9914,7 +9926,7 @@
       <c r="I60" t="n">
         <v>1.04</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="K60" t="n">
@@ -9927,13 +9939,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9960,7 +9972,7 @@
       <c r="I61" t="n">
         <v>1.55</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K61" t="n">
@@ -9973,13 +9985,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10006,7 +10018,7 @@
       <c r="I62" t="n">
         <v>1.080000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="K62" t="n">
@@ -10019,13 +10031,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10052,7 +10064,7 @@
       <c r="I63" t="n">
         <v>0.9700000000000005</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K63" t="n">
@@ -10065,13 +10077,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10098,7 +10110,7 @@
       <c r="I64" t="n">
         <v>0.9600000000000006</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K64" t="n">
@@ -10111,13 +10123,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10144,7 +10156,7 @@
       <c r="I65" t="n">
         <v>0.8800000000000006</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="K65" t="n">
@@ -10157,13 +10169,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10190,7 +10202,7 @@
       <c r="I66" t="n">
         <v>1.46</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="K66" t="n">
@@ -10203,13 +10215,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10236,7 +10248,7 @@
       <c r="I67" t="n">
         <v>1.25</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="K67" t="n">
@@ -10249,13 +10261,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10282,7 +10294,7 @@
       <c r="I68" t="n">
         <v>0.7800000000000004</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K68" t="n">
@@ -10295,13 +10307,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10328,7 +10340,7 @@
       <c r="I69" t="n">
         <v>1.16</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="K69" t="n">
@@ -10341,13 +10353,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10374,7 +10386,7 @@
       <c r="I70" t="n">
         <v>-2.06</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K70" t="n">
@@ -10387,13 +10399,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10420,7 +10432,7 @@
       <c r="I71" t="n">
         <v>-1.55</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K71" t="n">
@@ -10433,13 +10445,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10460,7 +10472,7 @@
       <c r="I72" t="n">
         <v>-1.87</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K72" t="n">
@@ -10498,57 +10510,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40022</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="C2" t="n">
@@ -10578,10 +10590,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C3" t="n">
@@ -10615,10 +10627,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39447</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C4" t="n">
@@ -10652,10 +10664,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C5" t="n">
@@ -10689,10 +10701,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C6" t="n">
@@ -10726,10 +10738,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C7" t="n">
@@ -10763,10 +10775,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C8" t="n">
@@ -10800,10 +10812,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C9" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C10" t="n">
@@ -10874,10 +10886,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C11" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C12" t="n">
@@ -10948,10 +10960,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C13" t="n">
@@ -10985,10 +10997,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C14" t="n">
@@ -11022,10 +11034,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="C15" t="n">
@@ -11059,10 +11071,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C16" t="n">
@@ -11096,10 +11108,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C17" t="n">
@@ -11133,10 +11145,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C18" t="n">
@@ -11170,10 +11182,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="C19" t="n">
@@ -11207,10 +11219,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C20" t="n">
@@ -11244,10 +11256,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="C21" t="n">
@@ -11281,10 +11293,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="C22" t="n">
@@ -11318,10 +11330,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41688</v>
       </c>
       <c r="C23" t="n">
@@ -11355,10 +11367,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C24" t="n">
@@ -11392,10 +11404,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C25" t="n">
@@ -11429,10 +11441,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="C26" t="n">
@@ -11466,10 +11478,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="C27" t="n">
@@ -11503,10 +11515,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="C28" t="n">
@@ -11540,10 +11552,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="C29" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="C30" t="n">
@@ -11614,10 +11626,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C31" t="n">
@@ -11651,10 +11663,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="C32" t="n">
@@ -11688,10 +11700,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C33" t="n">
@@ -11725,10 +11737,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="C34" t="n">
@@ -11762,10 +11774,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="C35" t="n">
@@ -11799,10 +11811,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C36" t="n">
@@ -11836,10 +11848,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="C37" t="n">
@@ -11873,10 +11885,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C38" t="n">
@@ -11910,10 +11922,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="C39" t="n">
@@ -11947,10 +11959,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C40" t="n">
@@ -11984,10 +11996,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C41" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="C42" t="n">
@@ -12058,10 +12070,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C43" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C44" t="n">
@@ -12132,10 +12144,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="C45" t="n">
@@ -12169,10 +12181,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="C46" t="n">
@@ -12206,10 +12218,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="C47" t="n">
@@ -12243,10 +12255,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C48" t="n">
@@ -12280,10 +12292,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C49" t="n">
@@ -12317,10 +12329,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C50" t="n">
@@ -12354,10 +12366,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="C51" t="n">
@@ -12391,10 +12403,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C52" t="n">
@@ -12428,10 +12440,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C53" t="n">
@@ -12465,10 +12477,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C54" t="n">
@@ -12502,10 +12514,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="C55" t="n">
@@ -12539,10 +12551,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C56" t="n">
@@ -12576,10 +12588,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C57" t="n">
@@ -12613,10 +12625,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C58" t="n">
@@ -12650,10 +12662,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="C59" t="n">
@@ -12687,10 +12699,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C60" t="n">
@@ -12724,10 +12736,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="C61" t="n">
@@ -12761,10 +12773,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C62" t="n">
@@ -12798,10 +12810,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45329</v>
       </c>
       <c r="C63" t="n">
@@ -12835,10 +12847,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C64" t="n">
@@ -12872,10 +12884,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C65" t="n">
@@ -12909,10 +12921,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="C66" t="n">
@@ -12946,10 +12958,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="C67" t="n">
@@ -12983,10 +12995,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="C68" t="n">
@@ -13020,10 +13032,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C69" t="n">
@@ -13057,10 +13069,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="C70" t="n">
@@ -13094,10 +13106,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="C71" t="n">
@@ -13131,10 +13143,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C72" t="n">
@@ -13186,12 +13198,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/F.xlsx
+++ b/salidas/empresas/F.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>3.878582239151001</v>
+        <v>3.87858247756958</v>
       </c>
       <c r="C3" t="n">
         <v>7.96999979019165</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>3.873715400695801</v>
+        <v>3.873716831207275</v>
       </c>
       <c r="C4" t="n">
         <v>7.960000038146973</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>3.429838895797729</v>
+        <v>3.429838180541992</v>
       </c>
       <c r="C5" t="n">
         <v>6.949999809265137</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>3.533473968505859</v>
+        <v>3.533474922180176</v>
       </c>
       <c r="C6" t="n">
         <v>7.159999847412109</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>3.419968366622925</v>
+        <v>3.419967174530029</v>
       </c>
       <c r="C7" t="n">
         <v>6.929999828338623</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>3.315720081329346</v>
+        <v>3.315719842910767</v>
       </c>
       <c r="C8" t="n">
         <v>6.670000076293945</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>4.160806179046631</v>
+        <v>4.160806655883789</v>
       </c>
       <c r="C9" t="n">
         <v>8.369999885559082</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>4.021614551544189</v>
+        <v>4.021615505218506</v>
       </c>
       <c r="C10" t="n">
         <v>8.090000152587891</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>4.11606502532959</v>
+        <v>4.116064071655273</v>
       </c>
       <c r="C11" t="n">
         <v>8.279999732971191</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>4.041499137878418</v>
+        <v>4.041500091552734</v>
       </c>
       <c r="C12" t="n">
         <v>8.130000114440918</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>3.7332923412323</v>
+        <v>3.733291625976562</v>
       </c>
       <c r="C13" t="n">
         <v>7.510000228881836</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>4.041499137878418</v>
+        <v>4.041500091552734</v>
       </c>
       <c r="C14" t="n">
         <v>8.130000114440918</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>3.932135820388794</v>
+        <v>3.932135343551636</v>
       </c>
       <c r="C15" t="n">
         <v>7.909999847412109</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>3.922192811965942</v>
+        <v>3.922194242477417</v>
       </c>
       <c r="C16" t="n">
         <v>7.889999866485596</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>3.996759176254272</v>
+        <v>3.996759653091431</v>
       </c>
       <c r="C17" t="n">
         <v>8.039999961853027</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>4.6827712059021</v>
+        <v>4.682770729064941</v>
       </c>
       <c r="C19" t="n">
         <v>9.420000076293945</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>3.882423400878906</v>
+        <v>3.882423877716064</v>
       </c>
       <c r="C21" t="n">
         <v>7.809999942779541</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>4.220458984375</v>
+        <v>4.220458030700684</v>
       </c>
       <c r="C22" t="n">
         <v>8.489999771118164</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>3.7332923412323</v>
+        <v>3.733291625976562</v>
       </c>
       <c r="C24" t="n">
         <v>7.510000228881836</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>3.345547199249268</v>
+        <v>3.345545768737793</v>
       </c>
       <c r="C25" t="n">
         <v>6.730000019073486</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>2.843466520309448</v>
+        <v>2.843464851379395</v>
       </c>
       <c r="C28" t="n">
         <v>5.71999979019165</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>4.106122970581055</v>
+        <v>4.106123447418213</v>
       </c>
       <c r="C29" t="n">
         <v>8.260000228881836</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>3.380344152450562</v>
+        <v>3.380342960357666</v>
       </c>
       <c r="C30" t="n">
         <v>6.800000190734863</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>2.391095876693726</v>
+        <v>2.391095638275146</v>
       </c>
       <c r="C31" t="n">
         <v>4.809999942779541</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>2.386125564575195</v>
+        <v>2.386125087738037</v>
       </c>
       <c r="C32" t="n">
         <v>4.800000190734863</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>2.584969520568848</v>
+        <v>2.584969043731689</v>
       </c>
       <c r="C34" t="n">
         <v>5.199999809265137</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>1.088669180870056</v>
+        <v>1.088669657707214</v>
       </c>
       <c r="C35" t="n">
         <v>2.190000057220459</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>1.33722448348999</v>
+        <v>1.337223768234253</v>
       </c>
       <c r="C36" t="n">
         <v>2.690000057220459</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>0.9295944571495056</v>
+        <v>0.9295945763587952</v>
       </c>
       <c r="C38" t="n">
         <v>1.870000004768372</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9942185282707214</v>
+        <v>0.994218647480011</v>
       </c>
       <c r="C39" t="n">
         <v>2</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>1.307397603988647</v>
+        <v>1.307397484779358</v>
       </c>
       <c r="C40" t="n">
         <v>2.630000114440918</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>2.972714185714722</v>
+        <v>2.972713470458984</v>
       </c>
       <c r="C41" t="n">
         <v>5.980000019073486</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>2.858378648757935</v>
+        <v>2.858378887176514</v>
       </c>
       <c r="C42" t="n">
         <v>5.75</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>3.017454385757446</v>
+        <v>3.01745343208313</v>
       </c>
       <c r="C43" t="n">
         <v>6.070000171661377</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>3.976874113082886</v>
+        <v>3.976874589920044</v>
       </c>
       <c r="C44" t="n">
         <v>8</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>3.778031587600708</v>
+        <v>3.778030872344971</v>
       </c>
       <c r="C45" t="n">
         <v>7.599999904632568</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>3.584158897399902</v>
+        <v>3.584157228469849</v>
       </c>
       <c r="C46" t="n">
         <v>7.210000038146973</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>3.479765176773071</v>
+        <v>3.47976541519165</v>
       </c>
       <c r="C47" t="n">
         <v>7</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>4.97109317779541</v>
+        <v>4.971094608306885</v>
       </c>
       <c r="C49" t="n">
         <v>10</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>5.388665199279785</v>
+        <v>5.388665676116943</v>
       </c>
       <c r="C50" t="n">
         <v>10.84000015258789</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>5.836064338684082</v>
+        <v>5.836063861846924</v>
       </c>
       <c r="C51" t="n">
         <v>11.73999977111816</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>6.248663902282715</v>
+        <v>6.248665332794189</v>
       </c>
       <c r="C52" t="n">
         <v>12.56999969482422</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>6.472362041473389</v>
+        <v>6.472364902496338</v>
       </c>
       <c r="C53" t="n">
         <v>13.02000045776367</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>5.831091403961182</v>
+        <v>5.831092357635498</v>
       </c>
       <c r="C54" t="n">
         <v>11.72999954223633</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>5.010862350463867</v>
+        <v>5.010861873626709</v>
       </c>
       <c r="C55" t="n">
         <v>10.07999992370605</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>6.348089218139648</v>
+        <v>6.348087787628174</v>
       </c>
       <c r="C56" t="n">
         <v>12.77000045776367</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>5.612365245819092</v>
+        <v>5.61236572265625</v>
       </c>
       <c r="C57" t="n">
         <v>11.28999996185303</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>6.084618091583252</v>
+        <v>6.08461856842041</v>
       </c>
       <c r="C58" t="n">
         <v>12.23999977111816</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>7.024156093597412</v>
+        <v>7.024154663085938</v>
       </c>
       <c r="C59" t="n">
         <v>14.13000011444092</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>8.346466064453125</v>
+        <v>8.346467018127441</v>
       </c>
       <c r="C61" t="n">
         <v>16.79000091552734</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>7.928893566131592</v>
+        <v>7.928895950317383</v>
       </c>
       <c r="C62" t="n">
         <v>15.94999980926514</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>7.481495380401611</v>
+        <v>7.481497764587402</v>
       </c>
       <c r="C63" t="n">
         <v>15.05000019073486</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>7.411902904510498</v>
+        <v>7.411903858184814</v>
       </c>
       <c r="C64" t="n">
         <v>14.90999984741211</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>7.690284252166748</v>
+        <v>7.690282821655273</v>
       </c>
       <c r="C65" t="n">
         <v>15.47000026702881</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>7.416871070861816</v>
+        <v>7.416871547698975</v>
       </c>
       <c r="C66" t="n">
         <v>14.92000007629395</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>6.855138301849365</v>
+        <v>6.855139255523682</v>
       </c>
       <c r="C67" t="n">
         <v>13.78999996185303</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>6.069705963134766</v>
+        <v>6.069705009460449</v>
       </c>
       <c r="C68" t="n">
         <v>12.21000003814697</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>5.52785587310791</v>
+        <v>5.527855396270752</v>
       </c>
       <c r="C69" t="n">
         <v>11.11999988555908</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>4.807046890258789</v>
+        <v>4.807044982910156</v>
       </c>
       <c r="C70" t="n">
         <v>9.670000076293945</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>5.806239128112793</v>
+        <v>5.80623722076416</v>
       </c>
       <c r="C71" t="n">
         <v>11.68000030517578</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>5.269359588623047</v>
+        <v>5.269360542297363</v>
       </c>
       <c r="C72" t="n">
         <v>10.60000038146973</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>5.348897933959961</v>
+        <v>5.348895072937012</v>
       </c>
       <c r="C73" t="n">
         <v>10.76000022888184</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>5.653770923614502</v>
+        <v>5.653769493103027</v>
       </c>
       <c r="C77" t="n">
         <v>11.27999973297119</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>4.806709289550781</v>
+        <v>4.80670690536499</v>
       </c>
       <c r="C79" t="n">
         <v>9.590000152587891</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>4.631280422210693</v>
+        <v>4.631279468536377</v>
       </c>
       <c r="C80" t="n">
         <v>9.239999771118164</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>4.706872463226318</v>
+        <v>4.706871509552002</v>
       </c>
       <c r="C81" t="n">
         <v>9.340000152587891</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>4.968924999237061</v>
+        <v>4.968923568725586</v>
       </c>
       <c r="C82" t="n">
         <v>9.859999656677246</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>5.651332855224609</v>
+        <v>5.651330471038818</v>
       </c>
       <c r="C83" t="n">
         <v>11.15999984741211</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>5.798186302185059</v>
+        <v>5.798184871673584</v>
       </c>
       <c r="C84" t="n">
         <v>11.44999980926514</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>6.557775020599365</v>
+        <v>6.557775497436523</v>
       </c>
       <c r="C85" t="n">
         <v>12.94999980926514</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>6.606064319610596</v>
+        <v>6.606065273284912</v>
       </c>
       <c r="C86" t="n">
         <v>12.94999980926514</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>6.432622909545898</v>
+        <v>6.432620525360107</v>
       </c>
       <c r="C87" t="n">
         <v>12.60999965667725</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>6.708085536956787</v>
+        <v>6.708086013793945</v>
       </c>
       <c r="C88" t="n">
         <v>13.14999961853027</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>6.993755340576172</v>
+        <v>6.993753433227539</v>
       </c>
       <c r="C89" t="n">
         <v>13.71000003814697</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>8.057463645935059</v>
+        <v>8.057464599609375</v>
       </c>
       <c r="C90" t="n">
         <v>15.68000030517578</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>8.725191116333008</v>
+        <v>8.725190162658691</v>
       </c>
       <c r="C92" t="n">
         <v>16.8799991607666</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>8.720020294189453</v>
+        <v>8.720022201538086</v>
       </c>
       <c r="C94" t="n">
         <v>16.8700008392334</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>8.894583702087402</v>
+        <v>8.894582748413086</v>
       </c>
       <c r="C95" t="n">
         <v>17.11000061035156</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>8.878990173339844</v>
+        <v>8.878988265991211</v>
       </c>
       <c r="C96" t="n">
         <v>17.07999992370605</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>8.021242141723633</v>
+        <v>8.021239280700684</v>
       </c>
       <c r="C97" t="n">
         <v>15.43000030517578</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>7.839247703552246</v>
+        <v>7.839248180389404</v>
       </c>
       <c r="C98" t="n">
         <v>14.96000003814697</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>8.064574241638184</v>
+        <v>8.064573287963867</v>
       </c>
       <c r="C99" t="n">
         <v>15.39000034332275</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>8.174614906311035</v>
+        <v>8.174617767333984</v>
       </c>
       <c r="C100" t="n">
         <v>15.60000038146973</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>8.528959274291992</v>
+        <v>8.528961181640625</v>
       </c>
       <c r="C101" t="n">
         <v>16.14999961853027</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>8.682113647460938</v>
+        <v>8.682112693786621</v>
       </c>
       <c r="C102" t="n">
         <v>16.44000053405762</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>9.10460090637207</v>
+        <v>9.104601860046387</v>
       </c>
       <c r="C103" t="n">
         <v>17.23999977111816</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>9.260261535644531</v>
+        <v>9.260260581970215</v>
       </c>
       <c r="C105" t="n">
         <v>17.40999984741211</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>7.561120986938477</v>
+        <v>7.561121463775635</v>
       </c>
       <c r="C107" t="n">
         <v>14.09000015258789</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>8.441194534301758</v>
+        <v>8.441196441650391</v>
       </c>
       <c r="C108" t="n">
         <v>15.72999954223633</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>8.317770004272461</v>
+        <v>8.317770957946777</v>
       </c>
       <c r="C109" t="n">
         <v>15.5</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>7.974380970001221</v>
+        <v>7.974381446838379</v>
       </c>
       <c r="C110" t="n">
         <v>14.71000003814697</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>8.858013153076172</v>
+        <v>8.858014106750488</v>
       </c>
       <c r="C111" t="n">
         <v>16.34000015258789</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>8.749591827392578</v>
+        <v>8.749593734741211</v>
       </c>
       <c r="C112" t="n">
         <v>16.13999938964844</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>8.646029472351074</v>
+        <v>8.646030426025391</v>
       </c>
       <c r="C113" t="n">
         <v>15.80000019073486</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>8.301284790039062</v>
+        <v>8.301281929016113</v>
       </c>
       <c r="C114" t="n">
         <v>15.17000007629395</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>8.213728904724121</v>
+        <v>8.213726997375488</v>
       </c>
       <c r="C115" t="n">
         <v>15.01000022888184</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>8.198151588439941</v>
+        <v>8.198150634765625</v>
       </c>
       <c r="C116" t="n">
         <v>14.82999992370605</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>7.667455196380615</v>
+        <v>7.66745662689209</v>
       </c>
       <c r="C117" t="n">
         <v>13.86999988555908</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>7.501611709594727</v>
+        <v>7.501612663269043</v>
       </c>
       <c r="C118" t="n">
         <v>13.56999969482422</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>8.002364158630371</v>
+        <v>8.002362251281738</v>
       </c>
       <c r="C120" t="n">
         <v>14.32999992370605</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>7.868337154388428</v>
+        <v>7.86833667755127</v>
       </c>
       <c r="C121" t="n">
         <v>14.09000015258789</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>6.892587184906006</v>
+        <v>6.892582416534424</v>
       </c>
       <c r="C122" t="n">
         <v>11.9399995803833</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>7.22162914276123</v>
+        <v>7.221627712249756</v>
       </c>
       <c r="C123" t="n">
         <v>12.51000022888184</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>7.793124198913574</v>
+        <v>7.793124675750732</v>
       </c>
       <c r="C124" t="n">
         <v>13.5</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>7.873239517211914</v>
+        <v>7.873242378234863</v>
       </c>
       <c r="C126" t="n">
         <v>13.48999977111816</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>7.336297035217285</v>
+        <v>7.336296558380127</v>
       </c>
       <c r="C127" t="n">
         <v>12.56999969482422</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>7.469842910766602</v>
+        <v>7.469841957092285</v>
       </c>
       <c r="C128" t="n">
         <v>12.65999984741211</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>7.434440612792969</v>
+        <v>7.434440135955811</v>
       </c>
       <c r="C129" t="n">
         <v>12.60000038146973</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>7.12172269821167</v>
+        <v>7.121722221374512</v>
       </c>
       <c r="C130" t="n">
         <v>12.06999969482422</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>7.013309955596924</v>
+        <v>7.013309478759766</v>
       </c>
       <c r="C131" t="n">
         <v>11.73999977111816</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>7.246289730072021</v>
+        <v>7.24628734588623</v>
       </c>
       <c r="C133" t="n">
         <v>12.13000011444092</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>7.502684593200684</v>
+        <v>7.502686023712158</v>
       </c>
       <c r="C134" t="n">
         <v>12.35999965667725</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>7.605876922607422</v>
+        <v>7.605875492095947</v>
       </c>
       <c r="C135" t="n">
         <v>12.52999973297119</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>7.065633773803711</v>
+        <v>7.065633296966553</v>
       </c>
       <c r="C136" t="n">
         <v>11.64000034332275</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>7.056278705596924</v>
+        <v>7.056275367736816</v>
       </c>
       <c r="C137" t="n">
         <v>11.47000026702881</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>6.840958595275879</v>
+        <v>6.840957164764404</v>
       </c>
       <c r="C138" t="n">
         <v>11.11999988555908</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>6.884020805358887</v>
+        <v>6.88401985168457</v>
       </c>
       <c r="C139" t="n">
         <v>11.1899995803833</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>6.991123199462891</v>
+        <v>6.991122245788574</v>
       </c>
       <c r="C140" t="n">
         <v>11.22000026702881</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>6.872732639312744</v>
+        <v>6.872734546661377</v>
       </c>
       <c r="C141" t="n">
         <v>11.02999973297119</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>7.458445072174072</v>
+        <v>7.458444118499756</v>
       </c>
       <c r="C142" t="n">
         <v>11.97000026702881</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>7.740305423736572</v>
+        <v>7.740308284759521</v>
       </c>
       <c r="C143" t="n">
         <v>12.27000045776367</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>7.898015022277832</v>
+        <v>7.898012638092041</v>
       </c>
       <c r="C144" t="n">
         <v>12.52000045776367</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>7.879087924957275</v>
+        <v>7.879087448120117</v>
       </c>
       <c r="C145" t="n">
         <v>12.48999977111816</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>7.090643882751465</v>
+        <v>7.090644359588623</v>
       </c>
       <c r="C146" t="n">
         <v>10.97000026702881</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>6.857951641082764</v>
+        <v>6.857952117919922</v>
       </c>
       <c r="C147" t="n">
         <v>10.60999965667725</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>7.161741733551025</v>
+        <v>7.161742687225342</v>
       </c>
       <c r="C148" t="n">
         <v>11.07999992370605</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>7.362636566162109</v>
+        <v>7.362638473510742</v>
       </c>
       <c r="C149" t="n">
         <v>11.23999977111816</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>7.565699577331543</v>
+        <v>7.565700054168701</v>
       </c>
       <c r="C150" t="n">
         <v>11.55000019073486</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>7.25128173828125</v>
+        <v>7.251281261444092</v>
       </c>
       <c r="C151" t="n">
         <v>11.06999969482422</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>6.297065258026123</v>
+        <v>6.297067165374756</v>
       </c>
       <c r="C153" t="n">
         <v>9.479999542236328</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>6.144290447235107</v>
+        <v>6.144289493560791</v>
       </c>
       <c r="C154" t="n">
         <v>9.25</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>6.457520008087158</v>
+        <v>6.457520484924316</v>
       </c>
       <c r="C155" t="n">
         <v>9.550000190734863</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>5.172779083251953</v>
+        <v>5.17277717590332</v>
       </c>
       <c r="C157" t="n">
         <v>7.650000095367432</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>6.033412456512451</v>
+        <v>6.033411979675293</v>
       </c>
       <c r="C159" t="n">
         <v>8.770000457763672</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>6.040290832519531</v>
+        <v>6.040291309356689</v>
       </c>
       <c r="C160" t="n">
         <v>8.779999732971191</v>
@@ -4636,7 +4636,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>6.654453754425049</v>
+        <v>6.654452800750732</v>
       </c>
       <c r="C162" t="n">
         <v>9.520000457763672</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>7.150739192962646</v>
+        <v>7.150741100311279</v>
       </c>
       <c r="C163" t="n">
         <v>10.22999954223633</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>6.760867595672607</v>
+        <v>6.760864734649658</v>
       </c>
       <c r="C164" t="n">
         <v>9.529999732971191</v>
@@ -4723,7 +4723,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>6.505472660064697</v>
+        <v>6.505472183227539</v>
       </c>
       <c r="C165" t="n">
         <v>9.170000076293945</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>6.498377323150635</v>
+        <v>6.498378276824951</v>
       </c>
       <c r="C166" t="n">
         <v>9.159999847412109</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>6.194013595581055</v>
+        <v>6.194014549255371</v>
       </c>
       <c r="C167" t="n">
         <v>8.590000152587891</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>6.532918453216553</v>
+        <v>6.532917499542236</v>
       </c>
       <c r="C168" t="n">
         <v>9.060000419616699</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>6.705974102020264</v>
+        <v>6.705974578857422</v>
       </c>
       <c r="C169" t="n">
         <v>9.300000190734863</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>6.468019485473633</v>
+        <v>6.468020915985107</v>
       </c>
       <c r="C170" t="n">
         <v>8.819999694824219</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>3.542011976242065</v>
+        <v>3.542011260986328</v>
       </c>
       <c r="C172" t="n">
         <v>4.829999923706055</v>
@@ -4955,7 +4955,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>3.732678174972534</v>
+        <v>3.732679605484009</v>
       </c>
       <c r="C173" t="n">
         <v>5.090000152587891</v>
@@ -4982,7 +4982,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>4.187346935272217</v>
+        <v>4.187347412109375</v>
       </c>
       <c r="C174" t="n">
         <v>5.710000038146973</v>
@@ -5009,7 +5009,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>4.458682060241699</v>
+        <v>4.458681106567383</v>
       </c>
       <c r="C175" t="n">
         <v>6.079999923706055</v>
@@ -5090,7 +5090,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>4.884015560150146</v>
+        <v>4.884016513824463</v>
       </c>
       <c r="C178" t="n">
         <v>6.659999847412109</v>
@@ -5117,7 +5117,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>5.668685436248779</v>
+        <v>5.668684959411621</v>
       </c>
       <c r="C179" t="n">
         <v>7.730000019073486</v>
@@ -5144,7 +5144,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>6.658689022064209</v>
+        <v>6.658688545227051</v>
       </c>
       <c r="C180" t="n">
         <v>9.079999923706055</v>
@@ -5225,7 +5225,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>8.580029487609863</v>
+        <v>8.580025672912598</v>
       </c>
       <c r="C183" t="n">
         <v>11.69999980926514</v>
@@ -5395,7 +5395,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>9.555365562438965</v>
+        <v>9.555364608764648</v>
       </c>
       <c r="C189" t="n">
         <v>13.02999973297119</v>
@@ -5424,7 +5424,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>10.38403224945068</v>
+        <v>10.38403511047363</v>
       </c>
       <c r="C190" t="n">
         <v>14.15999984741211</v>
@@ -5453,7 +5453,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>12.52537250518799</v>
+        <v>12.52537536621094</v>
       </c>
       <c r="C191" t="n">
         <v>17.07999992370605</v>
@@ -5482,7 +5482,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>14.14357376098633</v>
+        <v>14.14357089996338</v>
       </c>
       <c r="C192" t="n">
         <v>19.19000053405762</v>
@@ -5511,7 +5511,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>15.30807685852051</v>
+        <v>15.30808067321777</v>
       </c>
       <c r="C193" t="n">
         <v>20.77000045776367</v>
@@ -5540,7 +5540,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>15.03859615325928</v>
+        <v>15.03859996795654</v>
       </c>
       <c r="C194" t="n">
         <v>20.29999923706055</v>
@@ -5569,7 +5569,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>13.00875663757324</v>
+        <v>13.00875473022461</v>
       </c>
       <c r="C195" t="n">
         <v>17.55999946594238</v>
@@ -5598,7 +5598,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>12.52722454071045</v>
+        <v>12.5272274017334</v>
       </c>
       <c r="C196" t="n">
         <v>16.90999984741211</v>
@@ -5627,7 +5627,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>10.55976963043213</v>
+        <v>10.55977058410645</v>
       </c>
       <c r="C197" t="n">
         <v>14.15999984741211</v>
@@ -5743,7 +5743,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>11.47852897644043</v>
+        <v>11.47852611541748</v>
       </c>
       <c r="C201" t="n">
         <v>15.23999977111816</v>
@@ -5772,7 +5772,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>8.435661315917969</v>
+        <v>8.435662269592285</v>
       </c>
       <c r="C202" t="n">
         <v>11.19999980926514</v>
@@ -5830,7 +5830,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>10.57869529724121</v>
+        <v>10.57869338989258</v>
       </c>
       <c r="C204" t="n">
         <v>13.89999961853027</v>
@@ -5859,7 +5859,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>8.851095199584961</v>
+        <v>8.851093292236328</v>
       </c>
       <c r="C205" t="n">
         <v>11.63000011444092</v>
@@ -5888,7 +5888,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>10.28188133239746</v>
+        <v>10.28188228607178</v>
       </c>
       <c r="C206" t="n">
         <v>13.51000022888184</v>
@@ -5917,7 +5917,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>9.765057563781738</v>
+        <v>9.765058517456055</v>
       </c>
       <c r="C207" t="n">
         <v>12.06999969482422</v>
@@ -5971,7 +5971,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>9.731383323669434</v>
+        <v>9.731385231018066</v>
       </c>
       <c r="C209" t="n">
         <v>11.88000011444092</v>
@@ -5998,7 +5998,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>9.829680442810059</v>
+        <v>9.829681396484375</v>
       </c>
       <c r="C210" t="n">
         <v>12</v>
@@ -6027,7 +6027,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>12.39358806610107</v>
+        <v>12.39358997344971</v>
       </c>
       <c r="C211" t="n">
         <v>15.13000011444092</v>
@@ -6056,7 +6056,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>10.93862819671631</v>
+        <v>10.93862724304199</v>
       </c>
       <c r="C212" t="n">
         <v>13.21000003814697</v>
@@ -6114,7 +6114,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>10.28446483612061</v>
+        <v>10.28446197509766</v>
       </c>
       <c r="C214" t="n">
         <v>12.42000007629395</v>
@@ -6172,7 +6172,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>8.628335952758789</v>
+        <v>8.628334045410156</v>
       </c>
       <c r="C216" t="n">
         <v>10.26000022888184</v>
@@ -6201,7 +6201,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>10.25140190124512</v>
+        <v>10.2514009475708</v>
       </c>
       <c r="C217" t="n">
         <v>12.1899995803833</v>
@@ -6317,7 +6317,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>10.4934663772583</v>
+        <v>10.49347019195557</v>
       </c>
       <c r="C221" t="n">
         <v>12.14999961853027</v>
@@ -6346,7 +6346,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>10.60343551635742</v>
+        <v>10.60343742370605</v>
       </c>
       <c r="C222" t="n">
         <v>12.13000011444092</v>
@@ -6375,7 +6375,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>10.96183776855469</v>
+        <v>10.96183681488037</v>
       </c>
       <c r="C223" t="n">
         <v>12.53999996185303</v>
@@ -6404,7 +6404,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>9.45829963684082</v>
+        <v>9.458300590515137</v>
       </c>
       <c r="C224" t="n">
         <v>10.81999969482422</v>
@@ -6433,7 +6433,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>9.934099197387695</v>
+        <v>9.934098243713379</v>
       </c>
       <c r="C225" t="n">
         <v>11.1899995803833</v>
@@ -6549,7 +6549,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>8.908293724060059</v>
+        <v>8.908294677734375</v>
       </c>
       <c r="C229" t="n">
         <v>9.899999618530273</v>
@@ -6578,7 +6578,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>9.070263862609863</v>
+        <v>9.07026481628418</v>
       </c>
       <c r="C230" t="n">
         <v>10.07999992370605</v>
@@ -6636,7 +6636,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>9.320217132568359</v>
+        <v>9.320216178894043</v>
       </c>
       <c r="C232" t="n">
         <v>10.02999973297119</v>
@@ -6694,7 +6694,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>9.786190032958984</v>
+        <v>9.786189079284668</v>
       </c>
       <c r="C234" t="n">
         <v>10.38000011444092</v>
@@ -6723,7 +6723,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>10.22930240631104</v>
+        <v>10.22930335998535</v>
       </c>
       <c r="C235" t="n">
         <v>10.85000038146973</v>
@@ -6955,7 +6955,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>13.7655200958252</v>
+        <v>13.76552104949951</v>
       </c>
       <c r="C243" t="n">
         <v>14.09000015258789</v>
@@ -6982,7 +6982,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>11.27424430847168</v>
+        <v>11.274245262146</v>
       </c>
       <c r="C244" t="n">
         <v>11.53999996185303</v>
@@ -7009,7 +7009,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>11.80180835723877</v>
+        <v>11.80180931091309</v>
       </c>
       <c r="C245" t="n">
         <v>12.07999992370605</v>
